--- a/entertainment_forms/014_online_popularity_survey--entertainment_forms.xlsx
+++ b/entertainment_forms/014_online_popularity_survey--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'13-24',_'label':_'13-24'}</t>
+          <t>13-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': '13-24', 'label': '13-24'}</t>
+          <t>13-24</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'25-44',_'label':_'25-44'}</t>
+          <t>25-44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': '25-44', 'label': '25-44'}</t>
+          <t>25-44</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'45-54',_'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': '45-54', 'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'55-64',_'label':_'55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': '55-64', 'label': '55-64'}</t>
+          <t>55-64</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_65,_'label':_65}</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 65, 'label': 65}</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'pizza',_'label':_'pizza'}</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'pizza', 'label': 'Pizza'}</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'sushi',_'label':_'sushi'}</t>
+          <t>sushi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'sushi', 'label': 'Sushi'}</t>
+          <t>Sushi</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'burger',_'label':_'burger'}</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'burger', 'label': 'Burger'}</t>
+          <t>Burger</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'social_media',_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'social_media', 'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'friends',_'label':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'friends', 'label': 'Friends'}</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'search_engine',_'label':_'search_engine'}</t>
+          <t>search_engine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'search_engine', 'label': 'Search engine'}</t>
+          <t>Search engine</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'word_of_mouth',_'label':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'word_of_mouth', 'label': 'Word of mouth'}</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'online_advertisement',_'label':_'online_advertisement'}</t>
+          <t>online_advertisement</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'online_advertisement', 'label': 'Online advertisement'}</t>
+          <t>Online advertisement</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'instagram',_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'instagram', 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'youtube',_'label':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'youtube', 'label': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'snapchat',_'label':_'snapchat'}</t>
+          <t>snapchat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'snapchat', 'label': 'Snapchat'}</t>
+          <t>Snapchat</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'linkedin',_'label':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'linkedin', 'label': 'LinkedIn'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
